--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3919,6 +3919,317 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120396740</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Uggle stenar, Uggle stenar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>506809</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6572184</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120396689</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90600</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Uggle stenar, Uggle stenar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>506819</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6572173</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120398017</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90989</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Rigidoporus corticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Uggle stenar, Uggle stenar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>506917</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6572176</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4028,10 +4028,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120396689</v>
+        <v>120398017</v>
       </c>
       <c r="B30" t="n">
-        <v>90600</v>
+        <v>90989</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4040,25 +4040,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>5321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rigidoporus corticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506819</v>
+        <v>506917</v>
       </c>
       <c r="R30" t="n">
-        <v>6572173</v>
+        <v>6572176</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4130,10 +4130,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120398017</v>
+        <v>120396689</v>
       </c>
       <c r="B31" t="n">
-        <v>90989</v>
+        <v>90600</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4142,25 +4142,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5321</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506917</v>
+        <v>506819</v>
       </c>
       <c r="R31" t="n">
-        <v>6572176</v>
+        <v>6572173</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -3921,10 +3921,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120396740</v>
+        <v>120396689</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>90600</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3937,42 +3937,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Uggle stenar, Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506809</v>
+        <v>506819</v>
       </c>
       <c r="R29" t="n">
-        <v>6572184</v>
+        <v>6572173</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4130,10 +4125,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120396689</v>
+        <v>120396740</v>
       </c>
       <c r="B31" t="n">
-        <v>90600</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4146,37 +4141,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Uggle stenar, Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506819</v>
+        <v>506809</v>
       </c>
       <c r="R31" t="n">
-        <v>6572173</v>
+        <v>6572184</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -3921,10 +3921,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120396689</v>
+        <v>120398017</v>
       </c>
       <c r="B29" t="n">
-        <v>90600</v>
+        <v>90989</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3933,25 +3933,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>5321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rigidoporus corticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506819</v>
+        <v>506917</v>
       </c>
       <c r="R29" t="n">
-        <v>6572173</v>
+        <v>6572176</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120398017</v>
+        <v>120396689</v>
       </c>
       <c r="B30" t="n">
-        <v>90989</v>
+        <v>90600</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4035,25 +4035,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5321</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506917</v>
+        <v>506819</v>
       </c>
       <c r="R30" t="n">
-        <v>6572176</v>
+        <v>6572173</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4235,10 +4235,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121271303</v>
+        <v>121271295</v>
       </c>
       <c r="B32" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506898</v>
+        <v>506847</v>
       </c>
       <c r="R32" t="n">
-        <v>6572181</v>
+        <v>6572418</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. mkt grov. På nordostsidan. Med fiskelina. Ett par bålar satta tillsammans.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Delad stam, bredvid rotvälta. Blandad vitalitet</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4383,10 +4383,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121271295</v>
+        <v>121271302</v>
       </c>
       <c r="B33" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506847</v>
+        <v>506942</v>
       </c>
       <c r="R33" t="n">
-        <v>6572418</v>
+        <v>6572200</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Delad stam, bredvid rotvälta. Blandad vitalitet</t>
+          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4531,10 +4531,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121271302</v>
+        <v>121271296</v>
       </c>
       <c r="B34" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506942</v>
+        <v>506846</v>
       </c>
       <c r="R34" t="n">
-        <v>6572200</v>
+        <v>6572534</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Vid stigen. Blandad vitalitet. 2 bålar under samma nät.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4682,7 +4682,7 @@
         <v>121271301</v>
       </c>
       <c r="B35" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4827,10 +4827,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121271296</v>
+        <v>121271303</v>
       </c>
       <c r="B36" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506846</v>
+        <v>506898</v>
       </c>
       <c r="R36" t="n">
-        <v>6572534</v>
+        <v>6572181</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Vid stigen. Blandad vitalitet. 2 bålar under samma nät.</t>
+          <t>Transplanterade bålar i kommunalt projekt. mkt grov. På nordostsidan. Med fiskelina. Ett par bålar satta tillsammans.</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4235,7 +4235,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121271295</v>
+        <v>121271296</v>
       </c>
       <c r="B32" t="n">
         <v>79682</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506847</v>
+        <v>506846</v>
       </c>
       <c r="R32" t="n">
-        <v>6572418</v>
+        <v>6572534</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Delad stam, bredvid rotvälta. Blandad vitalitet</t>
+          <t>Transplanterade bålar i kommunalt projekt. Vid stigen. Blandad vitalitet. 2 bålar under samma nät.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4531,7 +4531,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121271296</v>
+        <v>121271301</v>
       </c>
       <c r="B34" t="n">
         <v>79682</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506846</v>
+        <v>506936</v>
       </c>
       <c r="R34" t="n">
-        <v>6572534</v>
+        <v>6572199</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Vid stigen. Blandad vitalitet. 2 bålar under samma nät.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4679,7 +4679,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121271301</v>
+        <v>121271295</v>
       </c>
       <c r="B35" t="n">
         <v>79682</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506936</v>
+        <v>506847</v>
       </c>
       <c r="R35" t="n">
-        <v>6572199</v>
+        <v>6572418</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Delad stam, bredvid rotvälta. Blandad vitalitet</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4238,7 +4238,7 @@
         <v>121271296</v>
       </c>
       <c r="B32" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121271302</v>
+        <v>121271301</v>
       </c>
       <c r="B33" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506942</v>
+        <v>506936</v>
       </c>
       <c r="R33" t="n">
-        <v>6572200</v>
+        <v>6572199</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4531,10 +4531,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121271301</v>
+        <v>121271302</v>
       </c>
       <c r="B34" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506936</v>
+        <v>506942</v>
       </c>
       <c r="R34" t="n">
-        <v>6572199</v>
+        <v>6572200</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4682,7 +4682,7 @@
         <v>121271295</v>
       </c>
       <c r="B35" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>121271303</v>
       </c>
       <c r="B36" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4235,7 +4235,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121271296</v>
+        <v>121271303</v>
       </c>
       <c r="B32" t="n">
         <v>79685</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506846</v>
+        <v>506898</v>
       </c>
       <c r="R32" t="n">
-        <v>6572534</v>
+        <v>6572181</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Vid stigen. Blandad vitalitet. 2 bålar under samma nät.</t>
+          <t>Transplanterade bålar i kommunalt projekt. mkt grov. På nordostsidan. Med fiskelina. Ett par bålar satta tillsammans.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4383,7 +4383,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121271301</v>
+        <v>121271296</v>
       </c>
       <c r="B33" t="n">
         <v>79685</v>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506936</v>
+        <v>506846</v>
       </c>
       <c r="R33" t="n">
-        <v>6572199</v>
+        <v>6572534</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Vid stigen. Blandad vitalitet. 2 bålar under samma nät.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4531,7 +4531,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121271302</v>
+        <v>121271295</v>
       </c>
       <c r="B34" t="n">
         <v>79685</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506942</v>
+        <v>506847</v>
       </c>
       <c r="R34" t="n">
-        <v>6572200</v>
+        <v>6572418</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Delad stam, bredvid rotvälta. Blandad vitalitet</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4679,7 +4679,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121271295</v>
+        <v>121271302</v>
       </c>
       <c r="B35" t="n">
         <v>79685</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506847</v>
+        <v>506942</v>
       </c>
       <c r="R35" t="n">
-        <v>6572418</v>
+        <v>6572200</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Delad stam, bredvid rotvälta. Blandad vitalitet</t>
+          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4827,7 +4827,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121271303</v>
+        <v>121271301</v>
       </c>
       <c r="B36" t="n">
         <v>79685</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506898</v>
+        <v>506936</v>
       </c>
       <c r="R36" t="n">
-        <v>6572181</v>
+        <v>6572199</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. mkt grov. På nordostsidan. Med fiskelina. Ett par bålar satta tillsammans.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4235,10 +4235,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121271303</v>
+        <v>121271302</v>
       </c>
       <c r="B32" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506898</v>
+        <v>506942</v>
       </c>
       <c r="R32" t="n">
-        <v>6572181</v>
+        <v>6572200</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. mkt grov. På nordostsidan. Med fiskelina. Ett par bålar satta tillsammans.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4386,7 +4386,7 @@
         <v>121271296</v>
       </c>
       <c r="B33" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>121271295</v>
       </c>
       <c r="B34" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4679,10 +4679,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121271302</v>
+        <v>121271303</v>
       </c>
       <c r="B35" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506942</v>
+        <v>506898</v>
       </c>
       <c r="R35" t="n">
-        <v>6572200</v>
+        <v>6572181</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
+          <t>Transplanterade bålar i kommunalt projekt. mkt grov. På nordostsidan. Med fiskelina. Ett par bålar satta tillsammans.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4830,7 +4830,7 @@
         <v>121271301</v>
       </c>
       <c r="B36" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4235,7 +4235,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121271302</v>
+        <v>121271296</v>
       </c>
       <c r="B32" t="n">
         <v>79688</v>
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506942</v>
+        <v>506846</v>
       </c>
       <c r="R32" t="n">
-        <v>6572200</v>
+        <v>6572534</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Vid stigen. Blandad vitalitet. 2 bålar under samma nät.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4383,7 +4383,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121271296</v>
+        <v>121271301</v>
       </c>
       <c r="B33" t="n">
         <v>79688</v>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506846</v>
+        <v>506936</v>
       </c>
       <c r="R33" t="n">
-        <v>6572534</v>
+        <v>6572199</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Vid stigen. Blandad vitalitet. 2 bålar under samma nät.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4531,7 +4531,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121271295</v>
+        <v>121271303</v>
       </c>
       <c r="B34" t="n">
         <v>79688</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506847</v>
+        <v>506898</v>
       </c>
       <c r="R34" t="n">
-        <v>6572418</v>
+        <v>6572181</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Delad stam, bredvid rotvälta. Blandad vitalitet</t>
+          <t>Transplanterade bålar i kommunalt projekt. mkt grov. På nordostsidan. Med fiskelina. Ett par bålar satta tillsammans.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4679,7 +4679,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121271303</v>
+        <v>121271295</v>
       </c>
       <c r="B35" t="n">
         <v>79688</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506898</v>
+        <v>506847</v>
       </c>
       <c r="R35" t="n">
-        <v>6572181</v>
+        <v>6572418</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. mkt grov. På nordostsidan. Med fiskelina. Ett par bålar satta tillsammans.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Delad stam, bredvid rotvälta. Blandad vitalitet</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4827,7 +4827,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121271301</v>
+        <v>121271302</v>
       </c>
       <c r="B36" t="n">
         <v>79688</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506936</v>
+        <v>506942</v>
       </c>
       <c r="R36" t="n">
-        <v>6572199</v>
+        <v>6572200</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4238,7 +4238,7 @@
         <v>121271296</v>
       </c>
       <c r="B32" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121271301</v>
+        <v>121271302</v>
       </c>
       <c r="B33" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506936</v>
+        <v>506942</v>
       </c>
       <c r="R33" t="n">
-        <v>6572199</v>
+        <v>6572200</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4531,10 +4531,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121271303</v>
+        <v>121271295</v>
       </c>
       <c r="B34" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506898</v>
+        <v>506847</v>
       </c>
       <c r="R34" t="n">
-        <v>6572181</v>
+        <v>6572418</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. mkt grov. På nordostsidan. Med fiskelina. Ett par bålar satta tillsammans.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Delad stam, bredvid rotvälta. Blandad vitalitet</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4679,10 +4679,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121271295</v>
+        <v>121271303</v>
       </c>
       <c r="B35" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506847</v>
+        <v>506898</v>
       </c>
       <c r="R35" t="n">
-        <v>6572418</v>
+        <v>6572181</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Delad stam, bredvid rotvälta. Blandad vitalitet</t>
+          <t>Transplanterade bålar i kommunalt projekt. mkt grov. På nordostsidan. Med fiskelina. Ett par bålar satta tillsammans.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4827,10 +4827,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121271302</v>
+        <v>121271301</v>
       </c>
       <c r="B36" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506942</v>
+        <v>506936</v>
       </c>
       <c r="R36" t="n">
-        <v>6572200</v>
+        <v>6572199</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4238,7 +4238,7 @@
         <v>121271296</v>
       </c>
       <c r="B32" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121271302</v>
+        <v>121271303</v>
       </c>
       <c r="B33" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506942</v>
+        <v>506898</v>
       </c>
       <c r="R33" t="n">
-        <v>6572200</v>
+        <v>6572181</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
+          <t>Transplanterade bålar i kommunalt projekt. mkt grov. På nordostsidan. Med fiskelina. Ett par bålar satta tillsammans.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4534,7 +4534,7 @@
         <v>121271295</v>
       </c>
       <c r="B34" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4679,10 +4679,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121271303</v>
+        <v>121271302</v>
       </c>
       <c r="B35" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506898</v>
+        <v>506942</v>
       </c>
       <c r="R35" t="n">
-        <v>6572181</v>
+        <v>6572200</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. mkt grov. På nordostsidan. Med fiskelina. Ett par bålar satta tillsammans.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4830,7 +4830,7 @@
         <v>121271301</v>
       </c>
       <c r="B36" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4235,7 +4235,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121271296</v>
+        <v>121271295</v>
       </c>
       <c r="B32" t="n">
         <v>79690</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506846</v>
+        <v>506847</v>
       </c>
       <c r="R32" t="n">
-        <v>6572534</v>
+        <v>6572418</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Vid stigen. Blandad vitalitet. 2 bålar under samma nät.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Delad stam, bredvid rotvälta. Blandad vitalitet</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4531,7 +4531,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121271295</v>
+        <v>121271302</v>
       </c>
       <c r="B34" t="n">
         <v>79690</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506847</v>
+        <v>506942</v>
       </c>
       <c r="R34" t="n">
-        <v>6572418</v>
+        <v>6572200</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Delad stam, bredvid rotvälta. Blandad vitalitet</t>
+          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4679,7 +4679,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121271302</v>
+        <v>121271301</v>
       </c>
       <c r="B35" t="n">
         <v>79690</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506942</v>
+        <v>506936</v>
       </c>
       <c r="R35" t="n">
-        <v>6572200</v>
+        <v>6572199</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4827,7 +4827,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121271301</v>
+        <v>121271296</v>
       </c>
       <c r="B36" t="n">
         <v>79690</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506936</v>
+        <v>506846</v>
       </c>
       <c r="R36" t="n">
-        <v>6572199</v>
+        <v>6572534</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Vid stigen. Blandad vitalitet. 2 bålar under samma nät.</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4383,7 +4383,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121271303</v>
+        <v>121271296</v>
       </c>
       <c r="B33" t="n">
         <v>79690</v>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506898</v>
+        <v>506846</v>
       </c>
       <c r="R33" t="n">
-        <v>6572181</v>
+        <v>6572534</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. mkt grov. På nordostsidan. Med fiskelina. Ett par bålar satta tillsammans.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Vid stigen. Blandad vitalitet. 2 bålar under samma nät.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4531,7 +4531,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121271302</v>
+        <v>121271303</v>
       </c>
       <c r="B34" t="n">
         <v>79690</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506942</v>
+        <v>506898</v>
       </c>
       <c r="R34" t="n">
-        <v>6572200</v>
+        <v>6572181</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
+          <t>Transplanterade bålar i kommunalt projekt. mkt grov. På nordostsidan. Med fiskelina. Ett par bålar satta tillsammans.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4679,7 +4679,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121271301</v>
+        <v>121271302</v>
       </c>
       <c r="B35" t="n">
         <v>79690</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506936</v>
+        <v>506942</v>
       </c>
       <c r="R35" t="n">
-        <v>6572199</v>
+        <v>6572200</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4827,7 +4827,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121271296</v>
+        <v>121271301</v>
       </c>
       <c r="B36" t="n">
         <v>79690</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506846</v>
+        <v>506936</v>
       </c>
       <c r="R36" t="n">
-        <v>6572534</v>
+        <v>6572199</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Vid stigen. Blandad vitalitet. 2 bålar under samma nät.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4235,7 +4235,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121271295</v>
+        <v>121271296</v>
       </c>
       <c r="B32" t="n">
         <v>79690</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506847</v>
+        <v>506846</v>
       </c>
       <c r="R32" t="n">
-        <v>6572418</v>
+        <v>6572534</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Delad stam, bredvid rotvälta. Blandad vitalitet</t>
+          <t>Transplanterade bålar i kommunalt projekt. Vid stigen. Blandad vitalitet. 2 bålar under samma nät.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4383,7 +4383,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121271296</v>
+        <v>121271302</v>
       </c>
       <c r="B33" t="n">
         <v>79690</v>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506846</v>
+        <v>506942</v>
       </c>
       <c r="R33" t="n">
-        <v>6572534</v>
+        <v>6572200</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Vid stigen. Blandad vitalitet. 2 bålar under samma nät.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4679,7 +4679,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121271302</v>
+        <v>121271301</v>
       </c>
       <c r="B35" t="n">
         <v>79690</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506942</v>
+        <v>506936</v>
       </c>
       <c r="R35" t="n">
-        <v>6572200</v>
+        <v>6572199</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Träd 2 och 3 står bredvid varandra. Unggranar behöver röjas.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4827,7 +4827,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121271301</v>
+        <v>121271295</v>
       </c>
       <c r="B36" t="n">
         <v>79690</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506936</v>
+        <v>506847</v>
       </c>
       <c r="R36" t="n">
-        <v>6572199</v>
+        <v>6572418</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Transplanterade bålar i kommunalt projekt. Intill träd 2. Ungran runtom. Många bålar med låg vitalitet.</t>
+          <t>Transplanterade bålar i kommunalt projekt. Delad stam, bredvid rotvälta. Blandad vitalitet</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4973,6 +4973,230 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122483741</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91246</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Uggle stenar, Uggle stenar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>506657</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6571751</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122483753</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90808</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Uggle stenar, Uggle stenar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>506657</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6571751</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4975,10 +4975,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483741</v>
+        <v>122483753</v>
       </c>
       <c r="B37" t="n">
-        <v>91246</v>
+        <v>90813</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4987,25 +4987,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5021,7 +5016,7 @@
         <v>6571751</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5087,10 +5082,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483753</v>
+        <v>122483741</v>
       </c>
       <c r="B38" t="n">
-        <v>90808</v>
+        <v>91251</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5099,25 +5094,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>1209</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5133,7 +5123,7 @@
         <v>6571751</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4975,10 +4975,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483753</v>
+        <v>122483741</v>
       </c>
       <c r="B37" t="n">
-        <v>90813</v>
+        <v>91264</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4987,20 +4987,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>1209</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5016,7 +5021,7 @@
         <v>6571751</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5082,10 +5087,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483741</v>
+        <v>122483753</v>
       </c>
       <c r="B38" t="n">
-        <v>91251</v>
+        <v>90826</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5094,20 +5099,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5123,7 +5133,7 @@
         <v>6571751</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4975,10 +4975,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483741</v>
+        <v>122483753</v>
       </c>
       <c r="B37" t="n">
-        <v>91264</v>
+        <v>90839</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4987,25 +4987,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5021,7 +5021,7 @@
         <v>6571751</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5087,10 +5087,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483753</v>
+        <v>122483741</v>
       </c>
       <c r="B38" t="n">
-        <v>90826</v>
+        <v>91277</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5099,25 +5099,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5133,7 +5133,7 @@
         <v>6571751</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4975,10 +4975,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483753</v>
+        <v>122483741</v>
       </c>
       <c r="B37" t="n">
-        <v>90839</v>
+        <v>91277</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4987,25 +4987,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5021,7 +5021,7 @@
         <v>6571751</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5087,10 +5087,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483741</v>
+        <v>122483753</v>
       </c>
       <c r="B38" t="n">
-        <v>91277</v>
+        <v>90839</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5099,25 +5099,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5133,7 +5133,7 @@
         <v>6571751</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5197,6 +5197,219 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122632202</v>
+      </c>
+      <c r="B39" t="n">
+        <v>90853</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Uggle stenar, Uggle stenar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>506849</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6572259</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122631867</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79641</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Uggle stenar, Uggle stenar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>506859</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6572127</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4978,7 +4978,7 @@
         <v>122483741</v>
       </c>
       <c r="B37" t="n">
-        <v>91277</v>
+        <v>91278</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>122483753</v>
       </c>
       <c r="B38" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122632202</v>
+        <v>122631867</v>
       </c>
       <c r="B39" t="n">
-        <v>90853</v>
+        <v>79641</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5211,50 +5211,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Uggle stenar, Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506849</v>
+        <v>506859</v>
       </c>
       <c r="R39" t="n">
-        <v>6572259</v>
+        <v>6572127</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5310,10 +5301,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122631867</v>
+        <v>122632202</v>
       </c>
       <c r="B40" t="n">
-        <v>79641</v>
+        <v>90853</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5322,41 +5313,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Uggle stenar, Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506859</v>
+        <v>506849</v>
       </c>
       <c r="R40" t="n">
-        <v>6572127</v>
+        <v>6572259</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4978,7 +4978,7 @@
         <v>122483741</v>
       </c>
       <c r="B37" t="n">
-        <v>91278</v>
+        <v>91279</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>122483753</v>
       </c>
       <c r="B38" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>122631867</v>
       </c>
       <c r="B39" t="n">
-        <v>79641</v>
+        <v>79642</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>122632202</v>
       </c>
       <c r="B40" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4975,10 +4975,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483741</v>
+        <v>122483753</v>
       </c>
       <c r="B37" t="n">
-        <v>91279</v>
+        <v>90837</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4987,25 +4987,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5021,7 +5021,7 @@
         <v>6571751</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5087,10 +5087,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483753</v>
+        <v>122483741</v>
       </c>
       <c r="B38" t="n">
-        <v>90834</v>
+        <v>91282</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5099,25 +5099,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5133,7 +5133,7 @@
         <v>6571751</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>122631867</v>
       </c>
       <c r="B39" t="n">
-        <v>79642</v>
+        <v>79645</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>122632202</v>
       </c>
       <c r="B40" t="n">
-        <v>90854</v>
+        <v>90857</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4975,10 +4975,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122483753</v>
+        <v>122483741</v>
       </c>
       <c r="B37" t="n">
-        <v>90837</v>
+        <v>91282</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4987,25 +4987,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5021,7 +5021,7 @@
         <v>6571751</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5087,10 +5087,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122483741</v>
+        <v>122483753</v>
       </c>
       <c r="B38" t="n">
-        <v>91282</v>
+        <v>90837</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5099,25 +5099,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5133,7 +5133,7 @@
         <v>6571751</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122631867</v>
+        <v>122632202</v>
       </c>
       <c r="B39" t="n">
-        <v>79645</v>
+        <v>90857</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5211,41 +5211,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Uggle stenar, Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506859</v>
+        <v>506849</v>
       </c>
       <c r="R39" t="n">
-        <v>6572127</v>
+        <v>6572259</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5301,10 +5310,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122632202</v>
+        <v>122631867</v>
       </c>
       <c r="B40" t="n">
-        <v>90857</v>
+        <v>79645</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5313,50 +5322,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Uggle stenar, Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506849</v>
+        <v>506859</v>
       </c>
       <c r="R40" t="n">
-        <v>6572259</v>
+        <v>6572127</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5410,6 +5410,354 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122734149</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90837</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>506877</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6572311</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Barbro Fehrm Friberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122733981</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79741</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>506878</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6572335</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Livskraftig ej transplantering.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Barbro Fehrm Friberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122728342</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79645</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Uggleområdet, Nrk</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>506897</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6572181</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>på grov asp</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Emil Åsegård</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Emil Åsegård</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -5199,10 +5199,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122632202</v>
+        <v>122631867</v>
       </c>
       <c r="B39" t="n">
-        <v>90960</v>
+        <v>79751</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5211,50 +5211,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Uggle stenar, Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506849</v>
+        <v>506859</v>
       </c>
       <c r="R39" t="n">
-        <v>6572259</v>
+        <v>6572127</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5310,10 +5301,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122631867</v>
+        <v>122632202</v>
       </c>
       <c r="B40" t="n">
-        <v>79747</v>
+        <v>90964</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5322,41 +5313,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Uggle stenar, Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506859</v>
+        <v>506849</v>
       </c>
       <c r="R40" t="n">
-        <v>6572127</v>
+        <v>6572259</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5412,10 +5412,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122728342</v>
+        <v>122734149</v>
       </c>
       <c r="B41" t="n">
-        <v>79747</v>
+        <v>90944</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5424,25 +5424,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5451,17 +5451,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Uggleområdet, Nrk</t>
+          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506897</v>
+        <v>506877</v>
       </c>
       <c r="R41" t="n">
-        <v>6572181</v>
+        <v>6572311</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5485,17 +5485,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>på grov asp</t>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5511,22 +5516,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122734149</v>
+        <v>122728342</v>
       </c>
       <c r="B42" t="n">
-        <v>90940</v>
+        <v>79751</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5535,25 +5540,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5562,17 +5567,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
+          <t>Uggleområdet, Nrk</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506877</v>
+        <v>506897</v>
       </c>
       <c r="R42" t="n">
-        <v>6572311</v>
+        <v>6572181</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5596,22 +5601,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>på grov asp</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5627,12 +5627,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Emil Åsegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
+          <t>Emil Åsegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5642,7 +5642,7 @@
         <v>122733981</v>
       </c>
       <c r="B43" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>122810497</v>
       </c>
       <c r="B44" t="n">
-        <v>90960</v>
+        <v>90964</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>122810508</v>
       </c>
       <c r="B45" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -4978,7 +4978,7 @@
         <v>122483741</v>
       </c>
       <c r="B37" t="n">
-        <v>91385</v>
+        <v>91389</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>122483753</v>
       </c>
       <c r="B38" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -5412,10 +5412,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122734149</v>
+        <v>122733981</v>
       </c>
       <c r="B41" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5428,21 +5428,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506877</v>
+        <v>506878</v>
       </c>
       <c r="R41" t="n">
-        <v>6572311</v>
+        <v>6572335</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5500,7 +5500,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Livskraftig ej transplantering.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5639,10 +5644,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122733981</v>
+        <v>122734149</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>90944</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5655,21 +5660,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5682,10 +5687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506878</v>
+        <v>506877</v>
       </c>
       <c r="R43" t="n">
-        <v>6572335</v>
+        <v>6572311</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5717,7 +5722,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5727,12 +5732,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Livskraftig ej transplantering.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -5412,10 +5412,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122733981</v>
+        <v>122734149</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>90944</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5428,21 +5428,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506878</v>
+        <v>506877</v>
       </c>
       <c r="R41" t="n">
-        <v>6572335</v>
+        <v>6572311</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5500,12 +5500,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Livskraftig ej transplantering.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5533,10 +5528,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122728342</v>
+        <v>122733981</v>
       </c>
       <c r="B42" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5545,25 +5540,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5572,17 +5567,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Uggleområdet, Nrk</t>
+          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506897</v>
+        <v>506878</v>
       </c>
       <c r="R42" t="n">
-        <v>6572181</v>
+        <v>6572335</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5606,17 +5601,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>på grov asp</t>
+          <t>Livskraftig ej transplantering.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5632,22 +5637,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122734149</v>
+        <v>122728342</v>
       </c>
       <c r="B43" t="n">
-        <v>90944</v>
+        <v>79751</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5656,25 +5661,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5683,17 +5688,17 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
+          <t>Uggleområdet, Nrk</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506877</v>
+        <v>506897</v>
       </c>
       <c r="R43" t="n">
-        <v>6572311</v>
+        <v>6572181</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5717,22 +5722,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>på grov asp</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5748,22 +5748,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Emil Åsegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
+          <t>Emil Åsegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122810497</v>
+        <v>122810508</v>
       </c>
       <c r="B44" t="n">
-        <v>90964</v>
+        <v>98357</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5772,49 +5772,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Barnmossen, Nrk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507012</v>
+        <v>507001</v>
       </c>
       <c r="R44" t="n">
-        <v>6572392</v>
+        <v>6572389</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5849,6 +5850,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5862,31 +5868,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # högt upp på stam och på grov gren # Pinus sylvestris # mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5904,10 +5885,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122810508</v>
+        <v>122810497</v>
       </c>
       <c r="B45" t="n">
-        <v>98355</v>
+        <v>90964</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5916,50 +5897,49 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Barnmossen, Nrk</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507001</v>
+        <v>507012</v>
       </c>
       <c r="R45" t="n">
-        <v>6572389</v>
+        <v>6572392</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5994,11 +5974,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>riklig</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6012,6 +5987,31 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # högt upp på stam och på grov gren # Pinus sylvestris # mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -5412,10 +5412,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122734149</v>
+        <v>122733981</v>
       </c>
       <c r="B41" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5428,21 +5428,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506877</v>
+        <v>506878</v>
       </c>
       <c r="R41" t="n">
-        <v>6572311</v>
+        <v>6572335</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5500,7 +5500,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Livskraftig ej transplantering.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5528,10 +5533,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122733981</v>
+        <v>122728342</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5540,25 +5545,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5567,17 +5572,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
+          <t>Uggleområdet, Nrk</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506878</v>
+        <v>506897</v>
       </c>
       <c r="R42" t="n">
-        <v>6572335</v>
+        <v>6572181</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5601,27 +5606,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Livskraftig ej transplantering.</t>
+          <t>på grov asp</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5637,22 +5632,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Emil Åsegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
+          <t>Emil Åsegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122728342</v>
+        <v>122734149</v>
       </c>
       <c r="B43" t="n">
-        <v>79751</v>
+        <v>90944</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5661,25 +5656,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5688,17 +5683,17 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Uggleområdet, Nrk</t>
+          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506897</v>
+        <v>506877</v>
       </c>
       <c r="R43" t="n">
-        <v>6572181</v>
+        <v>6572311</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5722,17 +5717,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>på grov asp</t>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5748,22 +5748,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122810508</v>
+        <v>122810497</v>
       </c>
       <c r="B44" t="n">
-        <v>98357</v>
+        <v>90964</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5772,50 +5772,49 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Barnmossen, Nrk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507001</v>
+        <v>507012</v>
       </c>
       <c r="R44" t="n">
-        <v>6572389</v>
+        <v>6572392</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5850,11 +5849,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>riklig</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5868,6 +5862,31 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # högt upp på stam och på grov gren # Pinus sylvestris # mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5885,10 +5904,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122810497</v>
+        <v>122810508</v>
       </c>
       <c r="B45" t="n">
-        <v>90964</v>
+        <v>98357</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5897,49 +5916,50 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Barnmossen, Nrk</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507012</v>
+        <v>507001</v>
       </c>
       <c r="R45" t="n">
-        <v>6572392</v>
+        <v>6572389</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5974,6 +5994,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5987,31 +6012,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # högt upp på stam och på grov gren # Pinus sylvestris # mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -5304,7 +5304,7 @@
         <v>122632202</v>
       </c>
       <c r="B40" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5533,10 +5533,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122728342</v>
+        <v>122734149</v>
       </c>
       <c r="B42" t="n">
-        <v>79751</v>
+        <v>90952</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5572,17 +5572,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Uggleområdet, Nrk</t>
+          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506897</v>
+        <v>506877</v>
       </c>
       <c r="R42" t="n">
-        <v>6572181</v>
+        <v>6572311</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5606,17 +5606,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>på grov asp</t>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5632,22 +5637,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122734149</v>
+        <v>122728342</v>
       </c>
       <c r="B43" t="n">
-        <v>90944</v>
+        <v>79751</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5656,25 +5661,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5683,17 +5688,17 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
+          <t>Uggleområdet, Nrk</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506877</v>
+        <v>506897</v>
       </c>
       <c r="R43" t="n">
-        <v>6572311</v>
+        <v>6572181</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5717,22 +5722,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>på grov asp</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5748,12 +5748,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Emil Åsegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
+          <t>Emil Åsegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5763,7 +5763,7 @@
         <v>122810497</v>
       </c>
       <c r="B44" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>122810508</v>
       </c>
       <c r="B45" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -5412,10 +5412,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122733981</v>
+        <v>122728342</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5424,25 +5424,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5451,17 +5451,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
+          <t>Uggleområdet, Nrk</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506878</v>
+        <v>506897</v>
       </c>
       <c r="R41" t="n">
-        <v>6572335</v>
+        <v>6572181</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5485,27 +5485,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Livskraftig ej transplantering.</t>
+          <t>på grov asp</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5521,22 +5511,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Emil Åsegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
+          <t>Emil Åsegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122734149</v>
+        <v>122733981</v>
       </c>
       <c r="B42" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5549,21 +5539,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5576,10 +5566,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506877</v>
+        <v>506878</v>
       </c>
       <c r="R42" t="n">
-        <v>6572311</v>
+        <v>6572335</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5611,7 +5601,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5621,7 +5611,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Livskraftig ej transplantering.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5649,10 +5644,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122728342</v>
+        <v>122734149</v>
       </c>
       <c r="B43" t="n">
-        <v>79751</v>
+        <v>90952</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5661,25 +5656,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5688,17 +5683,17 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Uggleområdet, Nrk</t>
+          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506897</v>
+        <v>506877</v>
       </c>
       <c r="R43" t="n">
-        <v>6572181</v>
+        <v>6572311</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5722,17 +5717,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>på grov asp</t>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5748,22 +5748,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122810497</v>
+        <v>122810508</v>
       </c>
       <c r="B44" t="n">
-        <v>90972</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5772,49 +5772,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Barnmossen, Nrk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507012</v>
+        <v>507001</v>
       </c>
       <c r="R44" t="n">
-        <v>6572392</v>
+        <v>6572389</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5849,6 +5850,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5862,31 +5868,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # högt upp på stam och på grov gren # Pinus sylvestris # mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5904,10 +5885,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122810508</v>
+        <v>122810497</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>90972</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5916,50 +5897,49 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Barnmossen, Nrk</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507001</v>
+        <v>507012</v>
       </c>
       <c r="R45" t="n">
-        <v>6572389</v>
+        <v>6572392</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5994,11 +5974,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>riklig</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6012,6 +5987,31 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # högt upp på stam och på grov gren # Pinus sylvestris # mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -5412,10 +5412,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122728342</v>
+        <v>122734149</v>
       </c>
       <c r="B41" t="n">
-        <v>79751</v>
+        <v>90952</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5424,25 +5424,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5451,17 +5451,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Uggleområdet, Nrk</t>
+          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506897</v>
+        <v>506877</v>
       </c>
       <c r="R41" t="n">
-        <v>6572181</v>
+        <v>6572311</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5485,17 +5485,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>på grov asp</t>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5511,22 +5516,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122733981</v>
+        <v>122728342</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5535,25 +5540,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5562,17 +5567,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
+          <t>Uggleområdet, Nrk</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506878</v>
+        <v>506897</v>
       </c>
       <c r="R42" t="n">
-        <v>6572335</v>
+        <v>6572181</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5596,27 +5601,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Livskraftig ej transplantering.</t>
+          <t>på grov asp</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5632,22 +5627,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Emil Åsegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
+          <t>Emil Åsegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122734149</v>
+        <v>122733981</v>
       </c>
       <c r="B43" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5660,21 +5655,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5687,10 +5682,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506877</v>
+        <v>506878</v>
       </c>
       <c r="R43" t="n">
-        <v>6572311</v>
+        <v>6572335</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5722,7 +5717,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5732,7 +5727,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Livskraftig ej transplantering.</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -5412,10 +5412,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122734149</v>
+        <v>122733981</v>
       </c>
       <c r="B41" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5428,21 +5428,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506877</v>
+        <v>506878</v>
       </c>
       <c r="R41" t="n">
-        <v>6572311</v>
+        <v>6572335</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5500,7 +5500,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Livskraftig ej transplantering.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5528,10 +5533,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122728342</v>
+        <v>122734149</v>
       </c>
       <c r="B42" t="n">
-        <v>79751</v>
+        <v>90952</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5540,25 +5545,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5567,17 +5572,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Uggleområdet, Nrk</t>
+          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506897</v>
+        <v>506877</v>
       </c>
       <c r="R42" t="n">
-        <v>6572181</v>
+        <v>6572311</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5601,17 +5606,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>på grov asp</t>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5627,22 +5637,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emil Åsegård</t>
+          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122733981</v>
+        <v>122728342</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5651,25 +5661,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5678,17 +5688,17 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Karlslundsskogen Örebro, Karlslundsskogen Örebro, Nrk</t>
+          <t>Uggleområdet, Nrk</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506878</v>
+        <v>506897</v>
       </c>
       <c r="R43" t="n">
-        <v>6572335</v>
+        <v>6572181</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5712,27 +5722,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Livskraftig ej transplantering.</t>
+          <t>på grov asp</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5748,12 +5748,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Emil Åsegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg, Lotta Sörman</t>
+          <t>Emil Åsegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -5415,7 +5415,7 @@
         <v>122733981</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>122734149</v>
       </c>
       <c r="B42" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>122728342</v>
       </c>
       <c r="B43" t="n">
-        <v>79751</v>
+        <v>79754</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5760,10 +5760,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122810508</v>
+        <v>122810497</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>90975</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5772,50 +5772,49 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Barnmossen, Nrk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507001</v>
+        <v>507012</v>
       </c>
       <c r="R44" t="n">
-        <v>6572389</v>
+        <v>6572392</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5850,11 +5849,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>riklig</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5868,6 +5862,31 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # högt upp på stam och på grov gren # Pinus sylvestris # mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5885,10 +5904,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122810497</v>
+        <v>122810508</v>
       </c>
       <c r="B45" t="n">
-        <v>90972</v>
+        <v>98368</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5897,49 +5916,50 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Barnmossen, Nrk</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507012</v>
+        <v>507001</v>
       </c>
       <c r="R45" t="n">
-        <v>6572392</v>
+        <v>6572389</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5974,6 +5994,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5987,31 +6012,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # högt upp på stam och på grov gren # Pinus sylvestris # mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -5412,10 +5412,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122733981</v>
+        <v>122734149</v>
       </c>
       <c r="B41" t="n">
-        <v>79850</v>
+        <v>90957</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5428,21 +5428,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506878</v>
+        <v>506877</v>
       </c>
       <c r="R41" t="n">
-        <v>6572335</v>
+        <v>6572311</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5500,12 +5500,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Livskraftig ej transplantering.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5533,10 +5528,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122734149</v>
+        <v>122733981</v>
       </c>
       <c r="B42" t="n">
-        <v>90955</v>
+        <v>79852</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5549,21 +5544,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5576,10 +5571,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506877</v>
+        <v>506878</v>
       </c>
       <c r="R42" t="n">
-        <v>6572311</v>
+        <v>6572335</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5611,7 +5606,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5621,7 +5616,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Livskraftig ej transplantering.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5652,7 +5652,7 @@
         <v>122728342</v>
       </c>
       <c r="B43" t="n">
-        <v>79754</v>
+        <v>79756</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5760,10 +5760,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122810497</v>
+        <v>122810508</v>
       </c>
       <c r="B44" t="n">
-        <v>90975</v>
+        <v>98370</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5772,49 +5772,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Barnmossen, Nrk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507012</v>
+        <v>507001</v>
       </c>
       <c r="R44" t="n">
-        <v>6572392</v>
+        <v>6572389</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5849,6 +5850,11 @@
           <t>2025-02-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5862,31 +5868,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # högt upp på stam och på grov gren # Pinus sylvestris # mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5904,10 +5885,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122810508</v>
+        <v>122810497</v>
       </c>
       <c r="B45" t="n">
-        <v>98368</v>
+        <v>90977</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5916,50 +5897,49 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Barnmossen, Nrk</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507001</v>
+        <v>507012</v>
       </c>
       <c r="R45" t="n">
-        <v>6572389</v>
+        <v>6572392</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5994,11 +5974,6 @@
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>riklig</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6012,6 +5987,31 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # högt upp på stam och på grov gren # Pinus sylvestris # mycket grov, spärrgrenig överståndare, säkerligen minst 250 år gammal</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 40725-2019 artfynd.xlsx
+++ b/artfynd/A 40725-2019 artfynd.xlsx
@@ -5763,7 +5763,7 @@
         <v>122810508</v>
       </c>
       <c r="B44" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>122810497</v>
       </c>
       <c r="B45" t="n">
-        <v>90977</v>
+        <v>90983</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
